--- a/機能設計書/CRUD図.xlsx
+++ b/機能設計書/CRUD図.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\OPENMEDIAVAULT\share\file_management_system\＠成果物\図\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FileManagementSystem_Doc\機能設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7805806A-FBD1-412A-B8CD-97728EB6A3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E7EF66-C291-4597-BDB8-7810670BD9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{23DE303E-3AA3-4C78-B8FE-2E0353E3B078}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="CRUD図" sheetId="11" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">CRUD図!$A$1:$AN$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">CRUD図!$A$1:$AR$28</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="34">
   <si>
     <t>CRUD図</t>
     <rPh sb="4" eb="5">
@@ -244,6 +244,17 @@
     <rPh sb="5" eb="7">
       <t>ヘンコウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外部ユーザーマスタ</t>
+    <rPh sb="0" eb="2">
+      <t>ガイブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>m_external_user</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -560,7 +571,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -623,63 +634,69 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -698,9 +715,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -719,9 +733,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -765,6 +776,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -790,9 +804,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -830,7 +844,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -936,7 +950,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1078,7 +1092,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1086,18 +1100,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98EF1578-3DFC-4788-A805-2D57EE52706D}">
-  <dimension ref="B2:AS43"/>
+  <dimension ref="B2:AW43"/>
   <sheetFormatPr defaultColWidth="3.33203125" defaultRowHeight="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="5" width="3.44140625" style="2" customWidth="1"/>
-    <col min="6" max="9" width="3.44140625" style="3" customWidth="1"/>
-    <col min="10" max="35" width="3.44140625" style="2" customWidth="1"/>
-    <col min="36" max="39" width="3.44140625" style="14" customWidth="1"/>
-    <col min="40" max="40" width="3.44140625" style="2" customWidth="1"/>
-    <col min="41" max="16384" width="3.33203125" style="2"/>
+    <col min="1" max="5" width="4.44140625" style="2" customWidth="1"/>
+    <col min="6" max="9" width="4.44140625" style="3" customWidth="1"/>
+    <col min="10" max="39" width="4.44140625" style="2" customWidth="1"/>
+    <col min="40" max="43" width="4.44140625" style="14" customWidth="1"/>
+    <col min="44" max="44" width="3.44140625" style="2" customWidth="1"/>
+    <col min="45" max="16384" width="3.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:41" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="69" t="s">
         <v>0</v>
       </c>
@@ -1113,7 +1127,7 @@
       <c r="L2" s="10"/>
       <c r="M2" s="10"/>
     </row>
-    <row r="3" spans="2:41" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="69"/>
       <c r="C3" s="69"/>
       <c r="D3" s="69"/>
@@ -1127,7 +1141,7 @@
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
     </row>
-    <row r="5" spans="2:41" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="55" t="s">
         <v>20</v>
       </c>
@@ -1155,37 +1169,43 @@
       <c r="R5" s="5"/>
       <c r="S5" s="6"/>
       <c r="T5" s="7" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="U5" s="5"/>
       <c r="V5" s="5"/>
       <c r="W5" s="6"/>
       <c r="X5" s="7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5"/>
       <c r="AA5" s="6"/>
       <c r="AB5" s="7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC5" s="5"/>
       <c r="AD5" s="5"/>
       <c r="AE5" s="6"/>
       <c r="AF5" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG5" s="5"/>
       <c r="AH5" s="5"/>
       <c r="AI5" s="6"/>
-      <c r="AJ5" s="18" t="s">
+      <c r="AJ5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK5" s="5"/>
+      <c r="AL5" s="5"/>
+      <c r="AM5" s="6"/>
+      <c r="AN5" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="AK5" s="19"/>
-      <c r="AL5" s="19"/>
-      <c r="AM5" s="20"/>
-    </row>
-    <row r="6" spans="2:41" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AO5" s="19"/>
+      <c r="AP5" s="19"/>
+      <c r="AQ5" s="20"/>
+    </row>
+    <row r="6" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="55"/>
       <c r="C6" s="55"/>
       <c r="D6" s="55"/>
@@ -1211,181 +1231,203 @@
       <c r="R6" s="5"/>
       <c r="S6" s="6"/>
       <c r="T6" s="7" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="U6" s="5"/>
       <c r="V6" s="5"/>
       <c r="W6" s="6"/>
       <c r="X6" s="7" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5"/>
       <c r="AA6" s="6"/>
       <c r="AB6" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC6" s="5"/>
       <c r="AD6" s="5"/>
       <c r="AE6" s="6"/>
       <c r="AF6" s="7" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="AG6" s="5"/>
       <c r="AH6" s="5"/>
       <c r="AI6" s="6"/>
-      <c r="AJ6" s="21" t="s">
+      <c r="AJ6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK6" s="5"/>
+      <c r="AL6" s="5"/>
+      <c r="AM6" s="6"/>
+      <c r="AN6" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="AK6" s="19"/>
-      <c r="AL6" s="19"/>
-      <c r="AM6" s="20"/>
-    </row>
-    <row r="7" spans="2:41" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AO6" s="19"/>
+      <c r="AP6" s="19"/>
+      <c r="AQ6" s="20"/>
+    </row>
+    <row r="7" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="55"/>
       <c r="C7" s="55"/>
       <c r="D7" s="55"/>
       <c r="E7" s="55"/>
       <c r="F7" s="55"/>
       <c r="G7" s="55"/>
-      <c r="H7" s="50" t="s">
+      <c r="H7" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="50" t="s">
+      <c r="I7" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="50" t="s">
+      <c r="J7" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="50" t="s">
+      <c r="K7" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="50" t="s">
+      <c r="L7" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="50" t="s">
+      <c r="M7" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="50" t="s">
+      <c r="N7" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="50" t="s">
+      <c r="O7" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="P7" s="50" t="s">
+      <c r="P7" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="Q7" s="50" t="s">
+      <c r="Q7" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="R7" s="50" t="s">
+      <c r="R7" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="S7" s="50" t="s">
+      <c r="S7" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="T7" s="50" t="s">
+      <c r="T7" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="U7" s="50" t="s">
+      <c r="U7" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="V7" s="50" t="s">
+      <c r="V7" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="W7" s="50" t="s">
+      <c r="W7" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="X7" s="50" t="s">
+      <c r="X7" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="Y7" s="50" t="s">
+      <c r="Y7" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="Z7" s="50" t="s">
+      <c r="Z7" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="AA7" s="50" t="s">
+      <c r="AA7" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="AB7" s="50" t="s">
+      <c r="AB7" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="AC7" s="50" t="s">
+      <c r="AC7" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="AD7" s="50" t="s">
+      <c r="AD7" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="AE7" s="50" t="s">
+      <c r="AE7" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="AF7" s="50" t="s">
+      <c r="AF7" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="AG7" s="50" t="s">
+      <c r="AG7" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="AH7" s="50" t="s">
+      <c r="AH7" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="AI7" s="50" t="s">
+      <c r="AI7" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="AJ7" s="50" t="s">
+      <c r="AJ7" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="AK7" s="50" t="s">
+      <c r="AK7" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="AL7" s="50" t="s">
+      <c r="AL7" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="AM7" s="50" t="s">
+      <c r="AM7" s="51" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="2:41" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AN7" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO7" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP7" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ7" s="51" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="56"/>
       <c r="C8" s="56"/>
       <c r="D8" s="56"/>
       <c r="E8" s="56"/>
       <c r="F8" s="56"/>
       <c r="G8" s="56"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="50"/>
-      <c r="P8" s="50"/>
-      <c r="Q8" s="50"/>
-      <c r="R8" s="50"/>
-      <c r="S8" s="50"/>
-      <c r="T8" s="50"/>
-      <c r="U8" s="50"/>
-      <c r="V8" s="50"/>
-      <c r="W8" s="50"/>
-      <c r="X8" s="50"/>
-      <c r="Y8" s="50"/>
-      <c r="Z8" s="50"/>
-      <c r="AA8" s="50"/>
-      <c r="AB8" s="50"/>
-      <c r="AC8" s="50"/>
-      <c r="AD8" s="50"/>
-      <c r="AE8" s="50"/>
-      <c r="AF8" s="50"/>
-      <c r="AG8" s="50"/>
-      <c r="AH8" s="50"/>
-      <c r="AI8" s="50"/>
-      <c r="AJ8" s="50"/>
-      <c r="AK8" s="50"/>
-      <c r="AL8" s="50"/>
-      <c r="AM8" s="50"/>
-    </row>
-    <row r="9" spans="2:41" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="51"/>
+      <c r="P8" s="51"/>
+      <c r="Q8" s="51"/>
+      <c r="R8" s="51"/>
+      <c r="S8" s="51"/>
+      <c r="T8" s="51"/>
+      <c r="U8" s="51"/>
+      <c r="V8" s="51"/>
+      <c r="W8" s="51"/>
+      <c r="X8" s="51"/>
+      <c r="Y8" s="51"/>
+      <c r="Z8" s="51"/>
+      <c r="AA8" s="51"/>
+      <c r="AB8" s="51"/>
+      <c r="AC8" s="51"/>
+      <c r="AD8" s="51"/>
+      <c r="AE8" s="51"/>
+      <c r="AF8" s="51"/>
+      <c r="AG8" s="51"/>
+      <c r="AH8" s="51"/>
+      <c r="AI8" s="51"/>
+      <c r="AJ8" s="51"/>
+      <c r="AK8" s="51"/>
+      <c r="AL8" s="51"/>
+      <c r="AM8" s="51"/>
+      <c r="AN8" s="51"/>
+      <c r="AO8" s="51"/>
+      <c r="AP8" s="51"/>
+      <c r="AQ8" s="51"/>
+    </row>
+    <row r="9" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="58" t="s">
         <v>12</v>
       </c>
@@ -1394,195 +1436,215 @@
       <c r="E9" s="59"/>
       <c r="F9" s="59"/>
       <c r="G9" s="60"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="22"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="N9" s="22"/>
-      <c r="O9" s="52"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="R9" s="22"/>
-      <c r="S9" s="22"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="V9" s="22"/>
-      <c r="W9" s="26"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z9" s="22"/>
-      <c r="AA9" s="22"/>
-      <c r="AB9" s="25"/>
-      <c r="AC9" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD9" s="22"/>
-      <c r="AE9" s="26"/>
-      <c r="AF9" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG9" s="22"/>
-      <c r="AH9" s="22"/>
-      <c r="AI9" s="22"/>
-      <c r="AJ9" s="65"/>
-      <c r="AK9" s="66"/>
-      <c r="AL9" s="66"/>
-      <c r="AM9" s="66"/>
-      <c r="AO9" s="14"/>
-    </row>
-    <row r="10" spans="2:41" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H9" s="54"/>
+      <c r="I9" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="24"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="N9" s="24"/>
+      <c r="O9" s="53"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="R9" s="24"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="24"/>
+      <c r="X9" s="26"/>
+      <c r="Y9" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="25"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD9" s="24"/>
+      <c r="AE9" s="24"/>
+      <c r="AF9" s="26"/>
+      <c r="AG9" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH9" s="24"/>
+      <c r="AI9" s="25"/>
+      <c r="AJ9" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK9" s="24"/>
+      <c r="AL9" s="24"/>
+      <c r="AM9" s="24"/>
+      <c r="AN9" s="65"/>
+      <c r="AO9" s="66"/>
+      <c r="AP9" s="66"/>
+      <c r="AQ9" s="66"/>
+      <c r="AS9" s="14"/>
+    </row>
+    <row r="10" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="61"/>
       <c r="C10" s="62"/>
       <c r="D10" s="62"/>
       <c r="E10" s="62"/>
       <c r="F10" s="62"/>
       <c r="G10" s="63"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="52"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="25"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="22"/>
-      <c r="W10" s="26"/>
-      <c r="X10" s="22"/>
-      <c r="Y10" s="22"/>
-      <c r="Z10" s="22"/>
-      <c r="AA10" s="22"/>
-      <c r="AB10" s="25"/>
-      <c r="AC10" s="22"/>
-      <c r="AD10" s="22"/>
-      <c r="AE10" s="26"/>
-      <c r="AF10" s="22"/>
-      <c r="AG10" s="22"/>
-      <c r="AH10" s="22"/>
-      <c r="AI10" s="22"/>
-      <c r="AJ10" s="65"/>
-      <c r="AK10" s="66"/>
-      <c r="AL10" s="66"/>
-      <c r="AM10" s="66"/>
-    </row>
-    <row r="11" spans="2:41" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="41" t="s">
+      <c r="H10" s="54"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="53"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="24"/>
+      <c r="V10" s="24"/>
+      <c r="W10" s="24"/>
+      <c r="X10" s="26"/>
+      <c r="Y10" s="24"/>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="25"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="24"/>
+      <c r="AD10" s="24"/>
+      <c r="AE10" s="24"/>
+      <c r="AF10" s="26"/>
+      <c r="AG10" s="24"/>
+      <c r="AH10" s="24"/>
+      <c r="AI10" s="25"/>
+      <c r="AJ10" s="24"/>
+      <c r="AK10" s="24"/>
+      <c r="AL10" s="24"/>
+      <c r="AM10" s="24"/>
+      <c r="AN10" s="65"/>
+      <c r="AO10" s="66"/>
+      <c r="AP10" s="66"/>
+      <c r="AQ10" s="66"/>
+    </row>
+    <row r="11" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="47" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="47"/>
-      <c r="K11" s="49"/>
-      <c r="L11" s="47" t="s">
-        <v>13</v>
-      </c>
-      <c r="M11" s="47" t="s">
-        <v>13</v>
-      </c>
-      <c r="N11" s="47"/>
-      <c r="O11" s="49"/>
-      <c r="P11" s="47"/>
-      <c r="Q11" s="47" t="s">
-        <v>13</v>
-      </c>
-      <c r="R11" s="47"/>
-      <c r="S11" s="47"/>
-      <c r="T11" s="51"/>
-      <c r="U11" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="V11" s="47"/>
-      <c r="W11" s="49"/>
-      <c r="X11" s="47"/>
-      <c r="Y11" s="47" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z11" s="47"/>
-      <c r="AA11" s="47"/>
-      <c r="AB11" s="51"/>
-      <c r="AC11" s="47" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD11" s="47"/>
-      <c r="AE11" s="49"/>
-      <c r="AF11" s="47" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG11" s="47"/>
-      <c r="AH11" s="47"/>
-      <c r="AI11" s="47"/>
-      <c r="AJ11" s="67"/>
-      <c r="AK11" s="64"/>
-      <c r="AL11" s="64"/>
-      <c r="AM11" s="64"/>
-    </row>
-    <row r="12" spans="2:41" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="44"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="27"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="38"/>
+      <c r="K11" s="50"/>
+      <c r="L11" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="N11" s="38"/>
+      <c r="O11" s="50"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="R11" s="38"/>
+      <c r="S11" s="38"/>
+      <c r="T11" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="U11" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="V11" s="38"/>
+      <c r="W11" s="38"/>
+      <c r="X11" s="52"/>
+      <c r="Y11" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z11" s="38"/>
+      <c r="AA11" s="50"/>
+      <c r="AB11" s="38"/>
+      <c r="AC11" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD11" s="38"/>
+      <c r="AE11" s="38"/>
+      <c r="AF11" s="52"/>
+      <c r="AG11" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH11" s="38"/>
+      <c r="AI11" s="50"/>
+      <c r="AJ11" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK11" s="38"/>
+      <c r="AL11" s="38"/>
+      <c r="AM11" s="38"/>
+      <c r="AN11" s="67"/>
+      <c r="AO11" s="64"/>
+      <c r="AP11" s="64"/>
+      <c r="AQ11" s="64"/>
+    </row>
+    <row r="12" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="35"/>
       <c r="J12" s="57"/>
-      <c r="K12" s="49"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="49"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="47"/>
-      <c r="T12" s="51"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="47"/>
-      <c r="W12" s="49"/>
-      <c r="X12" s="47"/>
-      <c r="Y12" s="47"/>
-      <c r="Z12" s="47"/>
-      <c r="AA12" s="47"/>
-      <c r="AB12" s="51"/>
-      <c r="AC12" s="47"/>
-      <c r="AD12" s="47"/>
-      <c r="AE12" s="49"/>
-      <c r="AF12" s="47"/>
-      <c r="AG12" s="47"/>
-      <c r="AH12" s="47"/>
-      <c r="AI12" s="47"/>
-      <c r="AJ12" s="67"/>
-      <c r="AK12" s="64"/>
-      <c r="AL12" s="64"/>
-      <c r="AM12" s="64"/>
-    </row>
-    <row r="13" spans="2:41" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K12" s="50"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="38"/>
+      <c r="Q12" s="38"/>
+      <c r="R12" s="38"/>
+      <c r="S12" s="38"/>
+      <c r="T12" s="38"/>
+      <c r="U12" s="38"/>
+      <c r="V12" s="38"/>
+      <c r="W12" s="38"/>
+      <c r="X12" s="52"/>
+      <c r="Y12" s="38"/>
+      <c r="Z12" s="38"/>
+      <c r="AA12" s="50"/>
+      <c r="AB12" s="38"/>
+      <c r="AC12" s="38"/>
+      <c r="AD12" s="38"/>
+      <c r="AE12" s="38"/>
+      <c r="AF12" s="52"/>
+      <c r="AG12" s="38"/>
+      <c r="AH12" s="38"/>
+      <c r="AI12" s="50"/>
+      <c r="AJ12" s="38"/>
+      <c r="AK12" s="38"/>
+      <c r="AL12" s="38"/>
+      <c r="AM12" s="38"/>
+      <c r="AN12" s="67"/>
+      <c r="AO12" s="64"/>
+      <c r="AP12" s="64"/>
+      <c r="AQ12" s="64"/>
+    </row>
+    <row r="13" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="58" t="s">
         <v>19</v>
       </c>
@@ -1591,682 +1653,746 @@
       <c r="E13" s="59"/>
       <c r="F13" s="59"/>
       <c r="G13" s="60"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="J13" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="K13" s="26"/>
-      <c r="L13" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="M13" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="N13" s="22"/>
-      <c r="O13" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
-      <c r="T13" s="25"/>
-      <c r="U13" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="V13" s="22"/>
-      <c r="W13" s="26"/>
-      <c r="X13" s="22"/>
-      <c r="Y13" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z13" s="22"/>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="68"/>
-      <c r="AC13" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD13" s="22"/>
-      <c r="AE13" s="26"/>
-      <c r="AF13" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG13" s="22"/>
-      <c r="AH13" s="22"/>
-      <c r="AI13" s="22"/>
-      <c r="AJ13" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="AK13" s="23" t="s">
-        <v>13</v>
-      </c>
+      <c r="H13" s="54"/>
+      <c r="I13" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="K13" s="25"/>
+      <c r="L13" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M13" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="N13" s="24"/>
+      <c r="O13" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="R13" s="24"/>
+      <c r="S13" s="24"/>
+      <c r="T13" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="U13" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="V13" s="24"/>
+      <c r="W13" s="24"/>
+      <c r="X13" s="26"/>
+      <c r="Y13" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z13" s="24"/>
+      <c r="AA13" s="25"/>
+      <c r="AB13" s="24"/>
+      <c r="AC13" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD13" s="24"/>
+      <c r="AE13" s="24"/>
+      <c r="AF13" s="68"/>
+      <c r="AG13" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH13" s="24"/>
+      <c r="AI13" s="25"/>
+      <c r="AJ13" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK13" s="24"/>
       <c r="AL13" s="24"/>
-      <c r="AM13" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="AO13" s="14"/>
-    </row>
-    <row r="14" spans="2:41" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AM13" s="24"/>
+      <c r="AN13" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO13" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP13" s="22"/>
+      <c r="AQ13" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS13" s="14"/>
+    </row>
+    <row r="14" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="61"/>
       <c r="C14" s="62"/>
       <c r="D14" s="62"/>
       <c r="E14" s="62"/>
       <c r="F14" s="62"/>
       <c r="G14" s="63"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="26"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="22"/>
-      <c r="S14" s="22"/>
-      <c r="T14" s="25"/>
-      <c r="U14" s="22"/>
-      <c r="V14" s="22"/>
-      <c r="W14" s="26"/>
-      <c r="X14" s="22"/>
-      <c r="Y14" s="36"/>
-      <c r="Z14" s="22"/>
-      <c r="AA14" s="22"/>
-      <c r="AB14" s="68"/>
-      <c r="AC14" s="36"/>
-      <c r="AD14" s="22"/>
-      <c r="AE14" s="26"/>
-      <c r="AF14" s="22"/>
-      <c r="AG14" s="22"/>
-      <c r="AH14" s="22"/>
-      <c r="AI14" s="22"/>
-      <c r="AJ14" s="23"/>
-      <c r="AK14" s="23"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="24"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="26"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="24"/>
+      <c r="AA14" s="25"/>
+      <c r="AB14" s="24"/>
+      <c r="AC14" s="33"/>
+      <c r="AD14" s="24"/>
+      <c r="AE14" s="24"/>
+      <c r="AF14" s="68"/>
+      <c r="AG14" s="33"/>
+      <c r="AH14" s="24"/>
+      <c r="AI14" s="25"/>
+      <c r="AJ14" s="24"/>
+      <c r="AK14" s="24"/>
       <c r="AL14" s="24"/>
-      <c r="AM14" s="23"/>
-      <c r="AO14" s="14"/>
-    </row>
-    <row r="15" spans="2:41" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="41" t="s">
+      <c r="AM14" s="24"/>
+      <c r="AN14" s="23"/>
+      <c r="AO14" s="23"/>
+      <c r="AP14" s="22"/>
+      <c r="AQ14" s="23"/>
+      <c r="AS14" s="14"/>
+    </row>
+    <row r="15" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="J15" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="K15" s="38"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="27"/>
-      <c r="O15" s="38"/>
-      <c r="P15" s="27"/>
-      <c r="Q15" s="27"/>
-      <c r="R15" s="27"/>
-      <c r="S15" s="27"/>
-      <c r="T15" s="37"/>
-      <c r="U15" s="27"/>
-      <c r="V15" s="27"/>
-      <c r="W15" s="38"/>
-      <c r="X15" s="27"/>
-      <c r="Y15" s="47"/>
-      <c r="Z15" s="27"/>
-      <c r="AA15" s="27"/>
-      <c r="AB15" s="48"/>
-      <c r="AC15" s="47"/>
-      <c r="AD15" s="27"/>
-      <c r="AE15" s="38"/>
-      <c r="AF15" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG15" s="27"/>
-      <c r="AH15" s="27"/>
-      <c r="AI15" s="27"/>
-      <c r="AJ15" s="28"/>
-      <c r="AK15" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="AL15" s="29"/>
-      <c r="AM15" s="28"/>
-      <c r="AO15" s="14"/>
-    </row>
-    <row r="16" spans="2:41" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="44"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
-      <c r="N16" s="27"/>
-      <c r="O16" s="38"/>
-      <c r="P16" s="27"/>
-      <c r="Q16" s="27"/>
-      <c r="R16" s="27"/>
-      <c r="S16" s="27"/>
-      <c r="T16" s="37"/>
-      <c r="U16" s="27"/>
-      <c r="V16" s="27"/>
-      <c r="W16" s="38"/>
-      <c r="X16" s="27"/>
-      <c r="Y16" s="47"/>
-      <c r="Z16" s="27"/>
-      <c r="AA16" s="27"/>
-      <c r="AB16" s="48"/>
-      <c r="AC16" s="47"/>
-      <c r="AD16" s="27"/>
-      <c r="AE16" s="38"/>
-      <c r="AF16" s="27"/>
-      <c r="AG16" s="27"/>
-      <c r="AH16" s="27"/>
-      <c r="AI16" s="27"/>
-      <c r="AJ16" s="28"/>
-      <c r="AK16" s="28"/>
-      <c r="AL16" s="29"/>
-      <c r="AM16" s="28"/>
-      <c r="AO16" s="14"/>
-    </row>
-    <row r="17" spans="2:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="30" t="s">
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="42"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="42"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="35"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="35"/>
+      <c r="U15" s="35"/>
+      <c r="V15" s="35"/>
+      <c r="W15" s="35"/>
+      <c r="X15" s="41"/>
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="35"/>
+      <c r="AA15" s="42"/>
+      <c r="AB15" s="35"/>
+      <c r="AC15" s="38"/>
+      <c r="AD15" s="35"/>
+      <c r="AE15" s="35"/>
+      <c r="AF15" s="49"/>
+      <c r="AG15" s="38"/>
+      <c r="AH15" s="35"/>
+      <c r="AI15" s="42"/>
+      <c r="AJ15" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK15" s="35"/>
+      <c r="AL15" s="35"/>
+      <c r="AM15" s="35"/>
+      <c r="AN15" s="39"/>
+      <c r="AO15" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP15" s="40"/>
+      <c r="AQ15" s="39"/>
+      <c r="AS15" s="14"/>
+    </row>
+    <row r="16" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="42"/>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="35"/>
+      <c r="U16" s="35"/>
+      <c r="V16" s="35"/>
+      <c r="W16" s="35"/>
+      <c r="X16" s="41"/>
+      <c r="Y16" s="35"/>
+      <c r="Z16" s="35"/>
+      <c r="AA16" s="42"/>
+      <c r="AB16" s="35"/>
+      <c r="AC16" s="38"/>
+      <c r="AD16" s="35"/>
+      <c r="AE16" s="35"/>
+      <c r="AF16" s="49"/>
+      <c r="AG16" s="38"/>
+      <c r="AH16" s="35"/>
+      <c r="AI16" s="42"/>
+      <c r="AJ16" s="35"/>
+      <c r="AK16" s="35"/>
+      <c r="AL16" s="35"/>
+      <c r="AM16" s="35"/>
+      <c r="AN16" s="39"/>
+      <c r="AO16" s="39"/>
+      <c r="AP16" s="40"/>
+      <c r="AQ16" s="39"/>
+      <c r="AS16" s="14"/>
+    </row>
+    <row r="17" spans="2:44" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22"/>
-      <c r="O17" s="26"/>
-      <c r="P17" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q17" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="R17" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="S17" s="22"/>
-      <c r="T17" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="U17" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="V17" s="22"/>
-      <c r="W17" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="X17" s="22"/>
-      <c r="Y17" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z17" s="22"/>
-      <c r="AA17" s="22"/>
-      <c r="AB17" s="25"/>
-      <c r="AC17" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD17" s="22"/>
-      <c r="AE17" s="26"/>
-      <c r="AF17" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG17" s="22"/>
-      <c r="AH17" s="22"/>
-      <c r="AI17" s="22"/>
-      <c r="AJ17" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="AK17" s="23" t="s">
-        <v>13</v>
-      </c>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q17" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="R17" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S17" s="24"/>
+      <c r="T17" s="24"/>
+      <c r="U17" s="70"/>
+      <c r="V17" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="W17" s="24"/>
+      <c r="X17" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y17" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z17" s="24"/>
+      <c r="AA17" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB17" s="24"/>
+      <c r="AC17" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD17" s="24"/>
+      <c r="AE17" s="24"/>
+      <c r="AF17" s="26"/>
+      <c r="AG17" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH17" s="24"/>
+      <c r="AI17" s="25"/>
+      <c r="AJ17" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK17" s="24"/>
       <c r="AL17" s="24"/>
-      <c r="AM17" s="23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="2:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="33"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="22"/>
-      <c r="Q18" s="22"/>
-      <c r="R18" s="22"/>
-      <c r="S18" s="22"/>
-      <c r="T18" s="25"/>
-      <c r="U18" s="22"/>
-      <c r="V18" s="22"/>
-      <c r="W18" s="26"/>
-      <c r="X18" s="22"/>
-      <c r="Y18" s="22"/>
-      <c r="Z18" s="22"/>
-      <c r="AA18" s="22"/>
-      <c r="AB18" s="25"/>
-      <c r="AC18" s="22"/>
-      <c r="AD18" s="22"/>
-      <c r="AE18" s="26"/>
-      <c r="AF18" s="22"/>
-      <c r="AG18" s="22"/>
-      <c r="AH18" s="22"/>
-      <c r="AI18" s="22"/>
-      <c r="AJ18" s="23"/>
-      <c r="AK18" s="23"/>
+      <c r="AM17" s="24"/>
+      <c r="AN17" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO17" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP17" s="22"/>
+      <c r="AQ17" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="2:44" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="30"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="24"/>
+      <c r="S18" s="24"/>
+      <c r="T18" s="24"/>
+      <c r="U18" s="34"/>
+      <c r="V18" s="24"/>
+      <c r="W18" s="24"/>
+      <c r="X18" s="26"/>
+      <c r="Y18" s="24"/>
+      <c r="Z18" s="24"/>
+      <c r="AA18" s="25"/>
+      <c r="AB18" s="24"/>
+      <c r="AC18" s="24"/>
+      <c r="AD18" s="24"/>
+      <c r="AE18" s="24"/>
+      <c r="AF18" s="26"/>
+      <c r="AG18" s="24"/>
+      <c r="AH18" s="24"/>
+      <c r="AI18" s="25"/>
+      <c r="AJ18" s="24"/>
+      <c r="AK18" s="24"/>
       <c r="AL18" s="24"/>
-      <c r="AM18" s="23"/>
-    </row>
-    <row r="19" spans="2:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="41" t="s">
+      <c r="AM18" s="24"/>
+      <c r="AN18" s="23"/>
+      <c r="AO18" s="23"/>
+      <c r="AP18" s="22"/>
+      <c r="AQ18" s="23"/>
+    </row>
+    <row r="19" spans="2:44" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="27"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="27"/>
-      <c r="O19" s="38"/>
-      <c r="P19" s="27"/>
-      <c r="Q19" s="27"/>
-      <c r="R19" s="27"/>
-      <c r="S19" s="27"/>
-      <c r="T19" s="37"/>
-      <c r="U19" s="27"/>
-      <c r="V19" s="27"/>
-      <c r="W19" s="38"/>
-      <c r="X19" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y19" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z19" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA19" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB19" s="37"/>
-      <c r="AC19" s="27"/>
-      <c r="AD19" s="27"/>
-      <c r="AE19" s="38"/>
-      <c r="AF19" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG19" s="27"/>
-      <c r="AH19" s="27"/>
-      <c r="AI19" s="27"/>
-      <c r="AJ19" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="AK19" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="AL19" s="29"/>
-      <c r="AM19" s="28" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="2:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="44"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="27"/>
-      <c r="R20" s="27"/>
-      <c r="S20" s="27"/>
-      <c r="T20" s="37"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="27"/>
-      <c r="W20" s="38"/>
-      <c r="X20" s="27"/>
-      <c r="Y20" s="27"/>
-      <c r="Z20" s="27"/>
-      <c r="AA20" s="27"/>
-      <c r="AB20" s="37"/>
-      <c r="AC20" s="27"/>
-      <c r="AD20" s="27"/>
-      <c r="AE20" s="38"/>
-      <c r="AF20" s="27"/>
-      <c r="AG20" s="27"/>
-      <c r="AH20" s="27"/>
-      <c r="AI20" s="27"/>
-      <c r="AJ20" s="28"/>
-      <c r="AK20" s="28"/>
-      <c r="AL20" s="29"/>
-      <c r="AM20" s="28"/>
-    </row>
-    <row r="21" spans="2:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="30" t="s">
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="42"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="35"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="35"/>
+      <c r="V19" s="35"/>
+      <c r="W19" s="35"/>
+      <c r="X19" s="41"/>
+      <c r="Y19" s="35"/>
+      <c r="Z19" s="35"/>
+      <c r="AA19" s="42"/>
+      <c r="AB19" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC19" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD19" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE19" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF19" s="41"/>
+      <c r="AG19" s="35"/>
+      <c r="AH19" s="35"/>
+      <c r="AI19" s="42"/>
+      <c r="AJ19" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK19" s="35"/>
+      <c r="AL19" s="35"/>
+      <c r="AM19" s="35"/>
+      <c r="AN19" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO19" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP19" s="40"/>
+      <c r="AQ19" s="39" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="2:44" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="46"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="42"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="35"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="35"/>
+      <c r="T20" s="35"/>
+      <c r="U20" s="35"/>
+      <c r="V20" s="35"/>
+      <c r="W20" s="35"/>
+      <c r="X20" s="41"/>
+      <c r="Y20" s="35"/>
+      <c r="Z20" s="35"/>
+      <c r="AA20" s="42"/>
+      <c r="AB20" s="35"/>
+      <c r="AC20" s="35"/>
+      <c r="AD20" s="35"/>
+      <c r="AE20" s="35"/>
+      <c r="AF20" s="41"/>
+      <c r="AG20" s="35"/>
+      <c r="AH20" s="35"/>
+      <c r="AI20" s="42"/>
+      <c r="AJ20" s="35"/>
+      <c r="AK20" s="35"/>
+      <c r="AL20" s="35"/>
+      <c r="AM20" s="35"/>
+      <c r="AN20" s="39"/>
+      <c r="AO20" s="39"/>
+      <c r="AP20" s="40"/>
+      <c r="AQ20" s="39"/>
+    </row>
+    <row r="21" spans="2:44" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="22"/>
-      <c r="N21" s="22"/>
-      <c r="O21" s="26"/>
-      <c r="P21" s="22"/>
-      <c r="Q21" s="22"/>
-      <c r="R21" s="22"/>
-      <c r="S21" s="22"/>
-      <c r="T21" s="25"/>
-      <c r="U21" s="22"/>
-      <c r="V21" s="22"/>
-      <c r="W21" s="26"/>
-      <c r="X21" s="22"/>
-      <c r="Y21" s="22"/>
-      <c r="Z21" s="22"/>
-      <c r="AA21" s="22"/>
-      <c r="AB21" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC21" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD21" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="AE21" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="AF21" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG21" s="22"/>
-      <c r="AH21" s="22"/>
-      <c r="AI21" s="22"/>
-      <c r="AJ21" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="AK21" s="23" t="s">
-        <v>13</v>
-      </c>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="24"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="24"/>
+      <c r="R21" s="24"/>
+      <c r="S21" s="24"/>
+      <c r="T21" s="24"/>
+      <c r="U21" s="24"/>
+      <c r="V21" s="24"/>
+      <c r="W21" s="24"/>
+      <c r="X21" s="26"/>
+      <c r="Y21" s="24"/>
+      <c r="Z21" s="24"/>
+      <c r="AA21" s="25"/>
+      <c r="AB21" s="24"/>
+      <c r="AC21" s="24"/>
+      <c r="AD21" s="24"/>
+      <c r="AE21" s="24"/>
+      <c r="AF21" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG21" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH21" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI21" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ21" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK21" s="24"/>
       <c r="AL21" s="24"/>
-      <c r="AM21" s="23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="2:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="33"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="26"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="22"/>
-      <c r="O22" s="26"/>
-      <c r="P22" s="22"/>
-      <c r="Q22" s="22"/>
-      <c r="R22" s="22"/>
-      <c r="S22" s="22"/>
-      <c r="T22" s="25"/>
-      <c r="U22" s="22"/>
-      <c r="V22" s="22"/>
-      <c r="W22" s="26"/>
-      <c r="X22" s="22"/>
-      <c r="Y22" s="22"/>
-      <c r="Z22" s="22"/>
-      <c r="AA22" s="22"/>
-      <c r="AB22" s="25"/>
-      <c r="AC22" s="22"/>
-      <c r="AD22" s="22"/>
-      <c r="AE22" s="26"/>
-      <c r="AF22" s="22"/>
-      <c r="AG22" s="22"/>
-      <c r="AH22" s="22"/>
-      <c r="AI22" s="22"/>
-      <c r="AJ22" s="23"/>
-      <c r="AK22" s="23"/>
+      <c r="AM21" s="24"/>
+      <c r="AN21" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO21" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP21" s="22"/>
+      <c r="AQ21" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="2:44" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="25"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
+      <c r="R22" s="24"/>
+      <c r="S22" s="24"/>
+      <c r="T22" s="24"/>
+      <c r="U22" s="24"/>
+      <c r="V22" s="24"/>
+      <c r="W22" s="24"/>
+      <c r="X22" s="26"/>
+      <c r="Y22" s="24"/>
+      <c r="Z22" s="24"/>
+      <c r="AA22" s="25"/>
+      <c r="AB22" s="24"/>
+      <c r="AC22" s="24"/>
+      <c r="AD22" s="24"/>
+      <c r="AE22" s="24"/>
+      <c r="AF22" s="26"/>
+      <c r="AG22" s="24"/>
+      <c r="AH22" s="24"/>
+      <c r="AI22" s="25"/>
+      <c r="AJ22" s="24"/>
+      <c r="AK22" s="24"/>
       <c r="AL22" s="24"/>
-      <c r="AM22" s="23"/>
-    </row>
-    <row r="23" spans="2:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="41" t="s">
+      <c r="AM22" s="24"/>
+      <c r="AN22" s="23"/>
+      <c r="AO22" s="23"/>
+      <c r="AP22" s="22"/>
+      <c r="AQ22" s="23"/>
+    </row>
+    <row r="23" spans="2:44" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="R23" s="27"/>
-      <c r="S23" s="39"/>
-      <c r="T23" s="37"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-      <c r="W23" s="38"/>
-      <c r="X23" s="27"/>
-      <c r="Y23" s="27"/>
-      <c r="Z23" s="27"/>
-      <c r="AA23" s="27"/>
-      <c r="AB23" s="37"/>
-      <c r="AC23" s="27"/>
-      <c r="AD23" s="27"/>
-      <c r="AE23" s="38"/>
-      <c r="AF23" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG23" s="27"/>
-      <c r="AH23" s="27"/>
-      <c r="AI23" s="27"/>
-      <c r="AJ23" s="28"/>
-      <c r="AK23" s="28"/>
-      <c r="AL23" s="29"/>
-      <c r="AM23" s="28"/>
-    </row>
-    <row r="24" spans="2:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="44"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="27"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="27"/>
-      <c r="O24" s="38"/>
-      <c r="P24" s="27"/>
-      <c r="Q24" s="27"/>
-      <c r="R24" s="27"/>
-      <c r="S24" s="40"/>
-      <c r="T24" s="37"/>
-      <c r="U24" s="27"/>
-      <c r="V24" s="27"/>
-      <c r="W24" s="38"/>
-      <c r="X24" s="27"/>
-      <c r="Y24" s="27"/>
-      <c r="Z24" s="27"/>
-      <c r="AA24" s="27"/>
-      <c r="AB24" s="37"/>
-      <c r="AC24" s="27"/>
-      <c r="AD24" s="27"/>
-      <c r="AE24" s="38"/>
-      <c r="AF24" s="27"/>
-      <c r="AG24" s="27"/>
-      <c r="AH24" s="27"/>
-      <c r="AI24" s="27"/>
-      <c r="AJ24" s="28"/>
-      <c r="AK24" s="28"/>
-      <c r="AL24" s="29"/>
-      <c r="AM24" s="28"/>
-    </row>
-    <row r="25" spans="2:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="30" t="s">
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="42"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R23" s="35"/>
+      <c r="S23" s="36"/>
+      <c r="T23" s="35"/>
+      <c r="U23" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="V23" s="35"/>
+      <c r="W23" s="36"/>
+      <c r="X23" s="41"/>
+      <c r="Y23" s="35"/>
+      <c r="Z23" s="35"/>
+      <c r="AA23" s="42"/>
+      <c r="AB23" s="35"/>
+      <c r="AC23" s="35"/>
+      <c r="AD23" s="35"/>
+      <c r="AE23" s="35"/>
+      <c r="AF23" s="41"/>
+      <c r="AG23" s="35"/>
+      <c r="AH23" s="35"/>
+      <c r="AI23" s="42"/>
+      <c r="AJ23" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK23" s="35"/>
+      <c r="AL23" s="35"/>
+      <c r="AM23" s="35"/>
+      <c r="AN23" s="39"/>
+      <c r="AO23" s="39"/>
+      <c r="AP23" s="40"/>
+      <c r="AQ23" s="39"/>
+    </row>
+    <row r="24" spans="2:44" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="46"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="35"/>
+      <c r="Q24" s="35"/>
+      <c r="R24" s="35"/>
+      <c r="S24" s="37"/>
+      <c r="T24" s="35"/>
+      <c r="U24" s="35"/>
+      <c r="V24" s="35"/>
+      <c r="W24" s="37"/>
+      <c r="X24" s="41"/>
+      <c r="Y24" s="35"/>
+      <c r="Z24" s="35"/>
+      <c r="AA24" s="42"/>
+      <c r="AB24" s="35"/>
+      <c r="AC24" s="35"/>
+      <c r="AD24" s="35"/>
+      <c r="AE24" s="35"/>
+      <c r="AF24" s="41"/>
+      <c r="AG24" s="35"/>
+      <c r="AH24" s="35"/>
+      <c r="AI24" s="42"/>
+      <c r="AJ24" s="35"/>
+      <c r="AK24" s="35"/>
+      <c r="AL24" s="35"/>
+      <c r="AM24" s="35"/>
+      <c r="AN24" s="39"/>
+      <c r="AO24" s="39"/>
+      <c r="AP24" s="40"/>
+      <c r="AQ24" s="39"/>
+    </row>
+    <row r="25" spans="2:44" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="26"/>
-      <c r="P25" s="22"/>
-      <c r="Q25" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="R25" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="S25" s="22"/>
-      <c r="T25" s="25"/>
-      <c r="U25" s="22"/>
-      <c r="V25" s="22"/>
-      <c r="W25" s="26"/>
-      <c r="X25" s="22"/>
-      <c r="Y25" s="22"/>
-      <c r="Z25" s="22"/>
-      <c r="AA25" s="22"/>
-      <c r="AB25" s="25"/>
-      <c r="AC25" s="22"/>
-      <c r="AD25" s="22"/>
-      <c r="AE25" s="26"/>
-      <c r="AF25" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG25" s="22"/>
-      <c r="AH25" s="22"/>
-      <c r="AI25" s="22"/>
-      <c r="AJ25" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="AK25" s="23" t="s">
-        <v>13</v>
-      </c>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="24"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="R25" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S25" s="24"/>
+      <c r="T25" s="24"/>
+      <c r="U25" s="26"/>
+      <c r="V25" s="24"/>
+      <c r="W25" s="24"/>
+      <c r="X25" s="26"/>
+      <c r="Y25" s="24"/>
+      <c r="Z25" s="24"/>
+      <c r="AA25" s="25"/>
+      <c r="AB25" s="24"/>
+      <c r="AC25" s="24"/>
+      <c r="AD25" s="24"/>
+      <c r="AE25" s="24"/>
+      <c r="AF25" s="26"/>
+      <c r="AG25" s="24"/>
+      <c r="AH25" s="24"/>
+      <c r="AI25" s="25"/>
+      <c r="AJ25" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK25" s="24"/>
       <c r="AL25" s="24"/>
-      <c r="AM25" s="23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="2:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="33"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="22"/>
-      <c r="O26" s="26"/>
-      <c r="P26" s="22"/>
-      <c r="Q26" s="25"/>
-      <c r="R26" s="22"/>
-      <c r="S26" s="22"/>
-      <c r="T26" s="25"/>
-      <c r="U26" s="22"/>
-      <c r="V26" s="22"/>
-      <c r="W26" s="26"/>
-      <c r="X26" s="22"/>
-      <c r="Y26" s="22"/>
-      <c r="Z26" s="22"/>
-      <c r="AA26" s="22"/>
-      <c r="AB26" s="25"/>
-      <c r="AC26" s="22"/>
-      <c r="AD26" s="22"/>
-      <c r="AE26" s="26"/>
-      <c r="AF26" s="22"/>
-      <c r="AG26" s="22"/>
-      <c r="AH26" s="22"/>
-      <c r="AI26" s="22"/>
-      <c r="AJ26" s="23"/>
-      <c r="AK26" s="23"/>
+      <c r="AM25" s="24"/>
+      <c r="AN25" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO25" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP25" s="22"/>
+      <c r="AQ25" s="23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="2:44" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="30"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="24"/>
+      <c r="M26" s="24"/>
+      <c r="N26" s="24"/>
+      <c r="O26" s="25"/>
+      <c r="P26" s="24"/>
+      <c r="Q26" s="26"/>
+      <c r="R26" s="24"/>
+      <c r="S26" s="24"/>
+      <c r="T26" s="24"/>
+      <c r="U26" s="26"/>
+      <c r="V26" s="24"/>
+      <c r="W26" s="24"/>
+      <c r="X26" s="26"/>
+      <c r="Y26" s="24"/>
+      <c r="Z26" s="24"/>
+      <c r="AA26" s="25"/>
+      <c r="AB26" s="24"/>
+      <c r="AC26" s="24"/>
+      <c r="AD26" s="24"/>
+      <c r="AE26" s="24"/>
+      <c r="AF26" s="26"/>
+      <c r="AG26" s="24"/>
+      <c r="AH26" s="24"/>
+      <c r="AI26" s="25"/>
+      <c r="AJ26" s="24"/>
+      <c r="AK26" s="24"/>
       <c r="AL26" s="24"/>
-      <c r="AM26" s="23"/>
-    </row>
-    <row r="27" spans="2:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AM26" s="24"/>
+      <c r="AN26" s="23"/>
+      <c r="AO26" s="23"/>
+      <c r="AP26" s="22"/>
+      <c r="AQ26" s="23"/>
+    </row>
+    <row r="27" spans="2:44" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -2297,8 +2423,12 @@
       <c r="AF27" s="1"/>
       <c r="AG27" s="1"/>
       <c r="AH27" s="1"/>
-    </row>
-    <row r="28" spans="2:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AI27" s="1"/>
+      <c r="AJ27" s="1"/>
+      <c r="AK27" s="1"/>
+      <c r="AL27" s="1"/>
+    </row>
+    <row r="28" spans="2:44" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -2332,8 +2462,12 @@
       <c r="AF28" s="1"/>
       <c r="AG28" s="1"/>
       <c r="AH28" s="1"/>
-    </row>
-    <row r="29" spans="2:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AI28" s="1"/>
+      <c r="AJ28" s="1"/>
+      <c r="AK28" s="1"/>
+      <c r="AL28" s="1"/>
+    </row>
+    <row r="29" spans="2:44" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
@@ -2367,10 +2501,14 @@
       <c r="AF29" s="1"/>
       <c r="AG29" s="1"/>
       <c r="AH29" s="1"/>
-      <c r="AL29" s="16"/>
-      <c r="AM29" s="16"/>
-    </row>
-    <row r="30" spans="2:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AI29" s="1"/>
+      <c r="AJ29" s="1"/>
+      <c r="AK29" s="1"/>
+      <c r="AL29" s="1"/>
+      <c r="AP29" s="16"/>
+      <c r="AQ29" s="16"/>
+    </row>
+    <row r="30" spans="2:44" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
@@ -2405,12 +2543,16 @@
       <c r="AG30" s="1"/>
       <c r="AH30" s="1"/>
       <c r="AI30" s="1"/>
-      <c r="AJ30" s="16"/>
-      <c r="AK30" s="16"/>
-      <c r="AL30" s="16"/>
-      <c r="AM30" s="16"/>
-    </row>
-    <row r="31" spans="2:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AJ30" s="1"/>
+      <c r="AK30" s="1"/>
+      <c r="AL30" s="1"/>
+      <c r="AM30" s="1"/>
+      <c r="AN30" s="16"/>
+      <c r="AO30" s="16"/>
+      <c r="AP30" s="16"/>
+      <c r="AQ30" s="16"/>
+    </row>
+    <row r="31" spans="2:44" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
@@ -2443,12 +2585,16 @@
       <c r="AG31" s="1"/>
       <c r="AH31" s="1"/>
       <c r="AI31" s="1"/>
-      <c r="AJ31" s="16"/>
-      <c r="AK31" s="16"/>
-      <c r="AL31" s="16"/>
-      <c r="AM31" s="16"/>
-    </row>
-    <row r="32" spans="2:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AJ31" s="1"/>
+      <c r="AK31" s="1"/>
+      <c r="AL31" s="1"/>
+      <c r="AM31" s="1"/>
+      <c r="AN31" s="16"/>
+      <c r="AO31" s="16"/>
+      <c r="AP31" s="16"/>
+      <c r="AQ31" s="16"/>
+    </row>
+    <row r="32" spans="2:44" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -2481,13 +2627,17 @@
       <c r="AG32" s="1"/>
       <c r="AH32" s="1"/>
       <c r="AI32" s="1"/>
-      <c r="AJ32" s="16"/>
-      <c r="AK32" s="16"/>
-      <c r="AL32" s="16"/>
-      <c r="AM32" s="16"/>
-      <c r="AN32" s="1"/>
-    </row>
-    <row r="33" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AJ32" s="1"/>
+      <c r="AK32" s="1"/>
+      <c r="AL32" s="1"/>
+      <c r="AM32" s="1"/>
+      <c r="AN32" s="16"/>
+      <c r="AO32" s="16"/>
+      <c r="AP32" s="16"/>
+      <c r="AQ32" s="16"/>
+      <c r="AR32" s="1"/>
+    </row>
+    <row r="33" spans="2:49" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
@@ -2512,20 +2662,24 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
       <c r="AA33" s="1"/>
+      <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
       <c r="AD33" s="1"/>
       <c r="AE33" s="1"/>
-      <c r="AF33" s="1"/>
       <c r="AG33" s="1"/>
       <c r="AH33" s="1"/>
       <c r="AI33" s="1"/>
-      <c r="AJ33" s="16"/>
-      <c r="AK33" s="16"/>
-      <c r="AL33" s="16"/>
-      <c r="AM33" s="16"/>
-      <c r="AN33" s="1"/>
-    </row>
-    <row r="34" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AJ33" s="1"/>
+      <c r="AK33" s="1"/>
+      <c r="AL33" s="1"/>
+      <c r="AM33" s="1"/>
+      <c r="AN33" s="16"/>
+      <c r="AO33" s="16"/>
+      <c r="AP33" s="16"/>
+      <c r="AQ33" s="16"/>
+      <c r="AR33" s="1"/>
+    </row>
+    <row r="34" spans="2:49" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="8"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -2560,12 +2714,16 @@
       <c r="AG34" s="1"/>
       <c r="AH34" s="1"/>
       <c r="AI34" s="1"/>
-      <c r="AJ34" s="16"/>
-      <c r="AK34" s="16"/>
-      <c r="AL34" s="16"/>
-      <c r="AM34" s="16"/>
-    </row>
-    <row r="35" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AJ34" s="1"/>
+      <c r="AK34" s="1"/>
+      <c r="AL34" s="1"/>
+      <c r="AM34" s="1"/>
+      <c r="AN34" s="16"/>
+      <c r="AO34" s="16"/>
+      <c r="AP34" s="16"/>
+      <c r="AQ34" s="16"/>
+    </row>
+    <row r="35" spans="2:49" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -2599,12 +2757,16 @@
       <c r="AG35" s="1"/>
       <c r="AH35" s="1"/>
       <c r="AI35" s="1"/>
-      <c r="AJ35" s="16"/>
-      <c r="AK35" s="16"/>
-      <c r="AL35" s="16"/>
-      <c r="AM35" s="16"/>
-    </row>
-    <row r="36" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AJ35" s="1"/>
+      <c r="AK35" s="1"/>
+      <c r="AL35" s="1"/>
+      <c r="AM35" s="1"/>
+      <c r="AN35" s="16"/>
+      <c r="AO35" s="16"/>
+      <c r="AP35" s="16"/>
+      <c r="AQ35" s="16"/>
+    </row>
+    <row r="36" spans="2:49" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="E36" s="1"/>
@@ -2626,14 +2788,14 @@
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
-    </row>
-    <row r="37" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y36" s="1"/>
+      <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
+      <c r="AB36" s="1"/>
+    </row>
+    <row r="37" spans="2:49" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="I37" s="2"/>
       <c r="J37" s="1"/>
-      <c r="Y37" s="1"/>
-      <c r="Z37" s="1"/>
-      <c r="AA37" s="1"/>
-      <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
       <c r="AD37" s="1"/>
       <c r="AE37" s="1"/>
@@ -2641,12 +2803,16 @@
       <c r="AG37" s="1"/>
       <c r="AH37" s="1"/>
       <c r="AI37" s="1"/>
-      <c r="AJ37" s="16"/>
-      <c r="AK37" s="16"/>
-      <c r="AL37" s="16"/>
-      <c r="AM37" s="16"/>
-    </row>
-    <row r="38" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AJ37" s="1"/>
+      <c r="AK37" s="1"/>
+      <c r="AL37" s="1"/>
+      <c r="AM37" s="1"/>
+      <c r="AN37" s="16"/>
+      <c r="AO37" s="16"/>
+      <c r="AP37" s="16"/>
+      <c r="AQ37" s="16"/>
+    </row>
+    <row r="38" spans="2:49" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E38" s="15"/>
       <c r="F38" s="12"/>
       <c r="G38" s="12"/>
@@ -2667,14 +2833,14 @@
       <c r="V38" s="13"/>
       <c r="W38" s="13"/>
       <c r="X38" s="13"/>
-    </row>
-    <row r="39" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y38" s="13"/>
+      <c r="Z38" s="13"/>
+      <c r="AA38" s="13"/>
+      <c r="AB38" s="13"/>
+    </row>
+    <row r="39" spans="2:49" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E39" s="14"/>
       <c r="I39" s="2"/>
-      <c r="Y39" s="13"/>
-      <c r="Z39" s="13"/>
-      <c r="AA39" s="13"/>
-      <c r="AB39" s="13"/>
       <c r="AC39" s="13"/>
       <c r="AD39" s="13"/>
       <c r="AE39" s="13"/>
@@ -2682,22 +2848,26 @@
       <c r="AG39" s="13"/>
       <c r="AH39" s="13"/>
       <c r="AI39" s="13"/>
-      <c r="AJ39" s="17"/>
-      <c r="AK39" s="17"/>
-      <c r="AL39" s="17"/>
-      <c r="AM39" s="17"/>
-      <c r="AN39" s="13"/>
-      <c r="AO39" s="13"/>
-      <c r="AP39" s="13"/>
-      <c r="AQ39" s="13"/>
+      <c r="AJ39" s="13"/>
+      <c r="AK39" s="13"/>
+      <c r="AL39" s="13"/>
+      <c r="AM39" s="13"/>
+      <c r="AN39" s="17"/>
+      <c r="AO39" s="17"/>
+      <c r="AP39" s="17"/>
+      <c r="AQ39" s="17"/>
       <c r="AR39" s="13"/>
       <c r="AS39" s="13"/>
-    </row>
-    <row r="40" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AT39" s="13"/>
+      <c r="AU39" s="13"/>
+      <c r="AV39" s="13"/>
+      <c r="AW39" s="13"/>
+    </row>
+    <row r="40" spans="2:49" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E40" s="14"/>
       <c r="I40" s="2"/>
     </row>
-    <row r="41" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:49" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E41" s="15"/>
       <c r="F41" s="12"/>
       <c r="G41" s="12"/>
@@ -2716,76 +2886,80 @@
       <c r="T41" s="11"/>
       <c r="U41" s="11"/>
       <c r="V41" s="11"/>
-    </row>
-    <row r="42" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="W41" s="11"/>
+      <c r="X41" s="11"/>
+      <c r="Y41" s="11"/>
+      <c r="Z41" s="11"/>
+    </row>
+    <row r="42" spans="2:49" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="I42" s="2"/>
     </row>
-    <row r="43" spans="2:45" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:49" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="I43" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="331">
-    <mergeCell ref="Z21:Z22"/>
+  <mergeCells count="371">
+    <mergeCell ref="AD21:AD22"/>
     <mergeCell ref="Q21:Q22"/>
-    <mergeCell ref="AF21:AF22"/>
     <mergeCell ref="AJ21:AJ22"/>
+    <mergeCell ref="AN21:AN22"/>
+    <mergeCell ref="AN19:AN20"/>
     <mergeCell ref="AJ19:AJ20"/>
-    <mergeCell ref="AF19:AF20"/>
-    <mergeCell ref="AL21:AL22"/>
-    <mergeCell ref="AM21:AM22"/>
+    <mergeCell ref="AP21:AP22"/>
+    <mergeCell ref="AQ21:AQ22"/>
     <mergeCell ref="B2:F3"/>
     <mergeCell ref="B13:G14"/>
     <mergeCell ref="B17:G18"/>
     <mergeCell ref="B19:G20"/>
     <mergeCell ref="B21:G22"/>
+    <mergeCell ref="AK21:AK22"/>
+    <mergeCell ref="AL21:AL22"/>
+    <mergeCell ref="AM21:AM22"/>
+    <mergeCell ref="AO21:AO22"/>
+    <mergeCell ref="AF21:AF22"/>
     <mergeCell ref="AG21:AG22"/>
     <mergeCell ref="AH21:AH22"/>
     <mergeCell ref="AI21:AI22"/>
-    <mergeCell ref="AK21:AK22"/>
+    <mergeCell ref="AA21:AA22"/>
     <mergeCell ref="AB21:AB22"/>
-    <mergeCell ref="AC21:AC22"/>
-    <mergeCell ref="AD21:AD22"/>
-    <mergeCell ref="AE21:AE22"/>
-    <mergeCell ref="W21:W22"/>
-    <mergeCell ref="X21:X22"/>
-    <mergeCell ref="AM19:AM20"/>
+    <mergeCell ref="AQ19:AQ20"/>
+    <mergeCell ref="AH19:AH20"/>
+    <mergeCell ref="AI19:AI20"/>
+    <mergeCell ref="AK19:AK20"/>
+    <mergeCell ref="AL19:AL20"/>
+    <mergeCell ref="AC19:AC20"/>
     <mergeCell ref="AD19:AD20"/>
     <mergeCell ref="AE19:AE20"/>
+    <mergeCell ref="AF19:AF20"/>
     <mergeCell ref="AG19:AG20"/>
-    <mergeCell ref="AH19:AH20"/>
-    <mergeCell ref="Y19:Y20"/>
-    <mergeCell ref="Z19:Z20"/>
-    <mergeCell ref="AA19:AA20"/>
-    <mergeCell ref="AB19:AB20"/>
-    <mergeCell ref="AC19:AC20"/>
     <mergeCell ref="H21:H22"/>
     <mergeCell ref="I21:I22"/>
     <mergeCell ref="J21:J22"/>
     <mergeCell ref="K21:K22"/>
     <mergeCell ref="L21:L22"/>
-    <mergeCell ref="AI19:AI20"/>
-    <mergeCell ref="AK19:AK20"/>
-    <mergeCell ref="AL19:AL20"/>
-    <mergeCell ref="T19:T20"/>
-    <mergeCell ref="U19:U20"/>
-    <mergeCell ref="V19:V20"/>
-    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="AM19:AM20"/>
+    <mergeCell ref="AO19:AO20"/>
+    <mergeCell ref="AP19:AP20"/>
     <mergeCell ref="X19:X20"/>
-    <mergeCell ref="AA21:AA22"/>
+    <mergeCell ref="Y19:Y20"/>
+    <mergeCell ref="Z19:Z20"/>
+    <mergeCell ref="AA19:AA20"/>
+    <mergeCell ref="AB19:AB20"/>
+    <mergeCell ref="AE21:AE22"/>
     <mergeCell ref="R21:R22"/>
     <mergeCell ref="S21:S22"/>
-    <mergeCell ref="T21:T22"/>
-    <mergeCell ref="U21:U22"/>
-    <mergeCell ref="V21:V22"/>
+    <mergeCell ref="X21:X22"/>
+    <mergeCell ref="Y21:Y22"/>
+    <mergeCell ref="Z21:Z22"/>
     <mergeCell ref="M21:M22"/>
     <mergeCell ref="N21:N22"/>
     <mergeCell ref="O21:O22"/>
     <mergeCell ref="P21:P22"/>
-    <mergeCell ref="Y21:Y22"/>
-    <mergeCell ref="AJ17:AJ18"/>
-    <mergeCell ref="AK17:AK18"/>
-    <mergeCell ref="AL17:AL18"/>
-    <mergeCell ref="AM17:AM18"/>
+    <mergeCell ref="AC21:AC22"/>
+    <mergeCell ref="AN17:AN18"/>
+    <mergeCell ref="AO17:AO18"/>
+    <mergeCell ref="AP17:AP18"/>
+    <mergeCell ref="AQ17:AQ18"/>
     <mergeCell ref="H19:H20"/>
     <mergeCell ref="I19:I20"/>
     <mergeCell ref="J19:J20"/>
@@ -2798,93 +2972,97 @@
     <mergeCell ref="Q19:Q20"/>
     <mergeCell ref="R19:R20"/>
     <mergeCell ref="S19:S20"/>
+    <mergeCell ref="AI17:AI18"/>
+    <mergeCell ref="AJ17:AJ18"/>
+    <mergeCell ref="AK17:AK18"/>
+    <mergeCell ref="AL17:AL18"/>
+    <mergeCell ref="AM17:AM18"/>
+    <mergeCell ref="AD17:AD18"/>
     <mergeCell ref="AE17:AE18"/>
     <mergeCell ref="AF17:AF18"/>
+    <mergeCell ref="N17:N18"/>
+    <mergeCell ref="O17:O18"/>
     <mergeCell ref="AG17:AG18"/>
     <mergeCell ref="AH17:AH18"/>
-    <mergeCell ref="AI17:AI18"/>
+    <mergeCell ref="Y17:Y18"/>
     <mergeCell ref="Z17:Z18"/>
     <mergeCell ref="AA17:AA18"/>
     <mergeCell ref="AB17:AB18"/>
-    <mergeCell ref="N17:N18"/>
-    <mergeCell ref="O17:O18"/>
     <mergeCell ref="AC17:AC18"/>
-    <mergeCell ref="AD17:AD18"/>
-    <mergeCell ref="U17:U18"/>
-    <mergeCell ref="V17:V18"/>
-    <mergeCell ref="W17:W18"/>
-    <mergeCell ref="X17:X18"/>
-    <mergeCell ref="Y17:Y18"/>
     <mergeCell ref="P17:P18"/>
     <mergeCell ref="Q17:Q18"/>
     <mergeCell ref="R17:R18"/>
     <mergeCell ref="S17:S18"/>
+    <mergeCell ref="X17:X18"/>
     <mergeCell ref="T17:T18"/>
+    <mergeCell ref="U17:U18"/>
+    <mergeCell ref="V17:V18"/>
+    <mergeCell ref="W17:W18"/>
+    <mergeCell ref="AQ13:AQ14"/>
+    <mergeCell ref="AI13:AI14"/>
+    <mergeCell ref="AJ13:AJ14"/>
+    <mergeCell ref="AK13:AK14"/>
+    <mergeCell ref="AL13:AL14"/>
     <mergeCell ref="AM13:AM14"/>
+    <mergeCell ref="AD13:AD14"/>
     <mergeCell ref="AE13:AE14"/>
     <mergeCell ref="AF13:AF14"/>
-    <mergeCell ref="AG13:AG14"/>
-    <mergeCell ref="AH13:AH14"/>
-    <mergeCell ref="AI13:AI14"/>
-    <mergeCell ref="Z13:Z14"/>
-    <mergeCell ref="AA13:AA14"/>
-    <mergeCell ref="AB13:AB14"/>
-    <mergeCell ref="Y13:Y14"/>
+    <mergeCell ref="AC13:AC14"/>
     <mergeCell ref="P13:P14"/>
     <mergeCell ref="Q13:Q14"/>
     <mergeCell ref="R13:R14"/>
     <mergeCell ref="S13:S14"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="AJ13:AJ14"/>
-    <mergeCell ref="AK13:AK14"/>
-    <mergeCell ref="AL13:AL14"/>
+    <mergeCell ref="X13:X14"/>
+    <mergeCell ref="AN13:AN14"/>
+    <mergeCell ref="AO13:AO14"/>
+    <mergeCell ref="AP13:AP14"/>
     <mergeCell ref="N13:N14"/>
     <mergeCell ref="O13:O14"/>
+    <mergeCell ref="AM11:AM12"/>
+    <mergeCell ref="AN11:AN12"/>
+    <mergeCell ref="AO11:AO12"/>
+    <mergeCell ref="AP11:AP12"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="Z11:Z12"/>
+    <mergeCell ref="AA11:AA12"/>
+    <mergeCell ref="AB11:AB12"/>
+    <mergeCell ref="AC11:AC12"/>
+    <mergeCell ref="AD11:AD12"/>
+    <mergeCell ref="AE11:AE12"/>
+    <mergeCell ref="AF11:AF12"/>
+    <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="AG13:AG14"/>
+    <mergeCell ref="AH13:AH14"/>
+    <mergeCell ref="Y13:Y14"/>
+    <mergeCell ref="Z13:Z14"/>
+    <mergeCell ref="AA13:AA14"/>
+    <mergeCell ref="AB13:AB14"/>
+    <mergeCell ref="AQ11:AQ12"/>
+    <mergeCell ref="AH11:AH12"/>
     <mergeCell ref="AI11:AI12"/>
     <mergeCell ref="AJ11:AJ12"/>
     <mergeCell ref="AK11:AK12"/>
     <mergeCell ref="AL11:AL12"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="R11:R12"/>
-    <mergeCell ref="V11:V12"/>
-    <mergeCell ref="W11:W12"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="Z11:Z12"/>
-    <mergeCell ref="AA11:AA12"/>
-    <mergeCell ref="AB11:AB12"/>
-    <mergeCell ref="AC11:AC12"/>
-    <mergeCell ref="AC13:AC14"/>
-    <mergeCell ref="AD13:AD14"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="V13:V14"/>
-    <mergeCell ref="W13:W14"/>
-    <mergeCell ref="X13:X14"/>
-    <mergeCell ref="AM11:AM12"/>
-    <mergeCell ref="AD11:AD12"/>
-    <mergeCell ref="AE11:AE12"/>
-    <mergeCell ref="AF11:AF12"/>
-    <mergeCell ref="AG11:AG12"/>
-    <mergeCell ref="AH11:AH12"/>
+    <mergeCell ref="AO7:AO8"/>
+    <mergeCell ref="AP7:AP8"/>
+    <mergeCell ref="AQ7:AQ8"/>
+    <mergeCell ref="AJ7:AJ8"/>
     <mergeCell ref="AK7:AK8"/>
     <mergeCell ref="AL7:AL8"/>
     <mergeCell ref="AM7:AM8"/>
-    <mergeCell ref="AF7:AF8"/>
-    <mergeCell ref="AG7:AG8"/>
-    <mergeCell ref="AH7:AH8"/>
-    <mergeCell ref="AI7:AI8"/>
-    <mergeCell ref="AJ7:AJ8"/>
-    <mergeCell ref="AE9:AE10"/>
-    <mergeCell ref="AF9:AF10"/>
-    <mergeCell ref="AG9:AG10"/>
-    <mergeCell ref="AH9:AH10"/>
+    <mergeCell ref="AN7:AN8"/>
     <mergeCell ref="AI9:AI10"/>
     <mergeCell ref="AJ9:AJ10"/>
     <mergeCell ref="AK9:AK10"/>
     <mergeCell ref="AL9:AL10"/>
     <mergeCell ref="AM9:AM10"/>
+    <mergeCell ref="AN9:AN10"/>
+    <mergeCell ref="AO9:AO10"/>
+    <mergeCell ref="AP9:AP10"/>
+    <mergeCell ref="AQ9:AQ10"/>
     <mergeCell ref="B5:G8"/>
     <mergeCell ref="B11:G12"/>
     <mergeCell ref="H11:H12"/>
@@ -2900,16 +3078,16 @@
     <mergeCell ref="N7:N8"/>
     <mergeCell ref="B9:G10"/>
     <mergeCell ref="N9:N10"/>
+    <mergeCell ref="AE7:AE8"/>
+    <mergeCell ref="AF7:AF8"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AH7:AH8"/>
+    <mergeCell ref="AI7:AI8"/>
+    <mergeCell ref="Z7:Z8"/>
     <mergeCell ref="AA7:AA8"/>
     <mergeCell ref="AB7:AB8"/>
     <mergeCell ref="AC7:AC8"/>
     <mergeCell ref="AD7:AD8"/>
-    <mergeCell ref="AE7:AE8"/>
-    <mergeCell ref="V7:V8"/>
-    <mergeCell ref="W7:W8"/>
-    <mergeCell ref="X7:X8"/>
-    <mergeCell ref="Y7:Y8"/>
-    <mergeCell ref="Z7:Z8"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="J13:J14"/>
@@ -2936,27 +3114,34 @@
     <mergeCell ref="Q7:Q8"/>
     <mergeCell ref="R7:R8"/>
     <mergeCell ref="S7:S8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="Y7:Y8"/>
     <mergeCell ref="S11:S12"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="O9:O10"/>
     <mergeCell ref="P9:P10"/>
     <mergeCell ref="Q9:Q10"/>
     <mergeCell ref="R9:R10"/>
     <mergeCell ref="S9:S10"/>
+    <mergeCell ref="X9:X10"/>
+    <mergeCell ref="Y9:Y10"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="V7:V8"/>
+    <mergeCell ref="W7:W8"/>
     <mergeCell ref="T9:T10"/>
     <mergeCell ref="U9:U10"/>
     <mergeCell ref="V9:V10"/>
-    <mergeCell ref="W9:W10"/>
-    <mergeCell ref="X9:X10"/>
-    <mergeCell ref="Y9:Y10"/>
     <mergeCell ref="Z9:Z10"/>
     <mergeCell ref="AA9:AA10"/>
     <mergeCell ref="AB9:AB10"/>
     <mergeCell ref="AC9:AC10"/>
     <mergeCell ref="AD9:AD10"/>
+    <mergeCell ref="AE9:AE10"/>
+    <mergeCell ref="AF9:AF10"/>
+    <mergeCell ref="AG9:AG10"/>
+    <mergeCell ref="AH9:AH10"/>
     <mergeCell ref="B15:G16"/>
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="I15:I16"/>
@@ -2970,26 +3155,30 @@
     <mergeCell ref="Q15:Q16"/>
     <mergeCell ref="R15:R16"/>
     <mergeCell ref="S15:S16"/>
+    <mergeCell ref="X15:X16"/>
+    <mergeCell ref="Y15:Y16"/>
+    <mergeCell ref="Z15:Z16"/>
+    <mergeCell ref="AA15:AA16"/>
+    <mergeCell ref="AB15:AB16"/>
     <mergeCell ref="T15:T16"/>
     <mergeCell ref="U15:U16"/>
     <mergeCell ref="V15:V16"/>
     <mergeCell ref="W15:W16"/>
-    <mergeCell ref="X15:X16"/>
-    <mergeCell ref="AH15:AH16"/>
-    <mergeCell ref="AI15:AI16"/>
-    <mergeCell ref="AJ15:AJ16"/>
-    <mergeCell ref="AK15:AK16"/>
     <mergeCell ref="AL15:AL16"/>
     <mergeCell ref="AM15:AM16"/>
-    <mergeCell ref="Y15:Y16"/>
-    <mergeCell ref="Z15:Z16"/>
-    <mergeCell ref="AA15:AA16"/>
-    <mergeCell ref="AB15:AB16"/>
+    <mergeCell ref="AN15:AN16"/>
+    <mergeCell ref="AO15:AO16"/>
+    <mergeCell ref="AP15:AP16"/>
+    <mergeCell ref="AQ15:AQ16"/>
     <mergeCell ref="AC15:AC16"/>
     <mergeCell ref="AD15:AD16"/>
     <mergeCell ref="AE15:AE16"/>
     <mergeCell ref="AF15:AF16"/>
     <mergeCell ref="AG15:AG16"/>
+    <mergeCell ref="AH15:AH16"/>
+    <mergeCell ref="AI15:AI16"/>
+    <mergeCell ref="AJ15:AJ16"/>
+    <mergeCell ref="AK15:AK16"/>
     <mergeCell ref="B23:G24"/>
     <mergeCell ref="H23:H24"/>
     <mergeCell ref="I23:I24"/>
@@ -3003,10 +3192,6 @@
     <mergeCell ref="Q23:Q24"/>
     <mergeCell ref="R23:R24"/>
     <mergeCell ref="S23:S24"/>
-    <mergeCell ref="T23:T24"/>
-    <mergeCell ref="U23:U24"/>
-    <mergeCell ref="V23:V24"/>
-    <mergeCell ref="W23:W24"/>
     <mergeCell ref="X23:X24"/>
     <mergeCell ref="Y23:Y24"/>
     <mergeCell ref="Z23:Z24"/>
@@ -3023,6 +3208,10 @@
     <mergeCell ref="AK23:AK24"/>
     <mergeCell ref="AL23:AL24"/>
     <mergeCell ref="AM23:AM24"/>
+    <mergeCell ref="AN23:AN24"/>
+    <mergeCell ref="AO23:AO24"/>
+    <mergeCell ref="AP23:AP24"/>
+    <mergeCell ref="AQ23:AQ24"/>
     <mergeCell ref="B25:G26"/>
     <mergeCell ref="H25:H26"/>
     <mergeCell ref="I25:I26"/>
@@ -3036,26 +3225,51 @@
     <mergeCell ref="Q25:Q26"/>
     <mergeCell ref="R25:R26"/>
     <mergeCell ref="S25:S26"/>
-    <mergeCell ref="T25:T26"/>
-    <mergeCell ref="U25:U26"/>
-    <mergeCell ref="V25:V26"/>
-    <mergeCell ref="W25:W26"/>
     <mergeCell ref="X25:X26"/>
-    <mergeCell ref="AH25:AH26"/>
-    <mergeCell ref="AI25:AI26"/>
-    <mergeCell ref="AJ25:AJ26"/>
-    <mergeCell ref="AK25:AK26"/>
-    <mergeCell ref="AL25:AL26"/>
-    <mergeCell ref="AM25:AM26"/>
     <mergeCell ref="Y25:Y26"/>
     <mergeCell ref="Z25:Z26"/>
     <mergeCell ref="AA25:AA26"/>
     <mergeCell ref="AB25:AB26"/>
+    <mergeCell ref="AL25:AL26"/>
+    <mergeCell ref="AM25:AM26"/>
+    <mergeCell ref="AN25:AN26"/>
+    <mergeCell ref="AO25:AO26"/>
+    <mergeCell ref="AP25:AP26"/>
+    <mergeCell ref="AQ25:AQ26"/>
     <mergeCell ref="AC25:AC26"/>
     <mergeCell ref="AD25:AD26"/>
     <mergeCell ref="AE25:AE26"/>
     <mergeCell ref="AF25:AF26"/>
     <mergeCell ref="AG25:AG26"/>
+    <mergeCell ref="AH25:AH26"/>
+    <mergeCell ref="AI25:AI26"/>
+    <mergeCell ref="AJ25:AJ26"/>
+    <mergeCell ref="AK25:AK26"/>
+    <mergeCell ref="W9:W10"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="V11:V12"/>
+    <mergeCell ref="W11:W12"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="V13:V14"/>
+    <mergeCell ref="W13:W14"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="T21:T22"/>
+    <mergeCell ref="U21:U22"/>
+    <mergeCell ref="V21:V22"/>
+    <mergeCell ref="W21:W22"/>
+    <mergeCell ref="T23:T24"/>
+    <mergeCell ref="U23:U24"/>
+    <mergeCell ref="V23:V24"/>
+    <mergeCell ref="W23:W24"/>
+    <mergeCell ref="T25:T26"/>
+    <mergeCell ref="U25:U26"/>
+    <mergeCell ref="V25:V26"/>
+    <mergeCell ref="W25:W26"/>
+    <mergeCell ref="T19:T20"/>
+    <mergeCell ref="U19:U20"/>
+    <mergeCell ref="V19:V20"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
